--- a/GameConfig/Datas/情绪记忆规则配置表.xlsx
+++ b/GameConfig/Datas/情绪记忆规则配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="情绪记忆规则配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情绪记忆规则配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -614,43 +614,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>M99</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>M98</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>OncePerRun</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameConfig/Datas/情绪记忆规则配置表.xlsx
+++ b/GameConfig/Datas/情绪记忆规则配置表.xlsx
@@ -416,14 +416,14 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19.8" customWidth="1" min="2" max="2"/>
-    <col width="19.8" customWidth="1" min="3" max="3"/>
-    <col width="37.40000000000001" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="17.6" customWidth="1" min="6" max="6"/>
-    <col width="26.4" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
